--- a/KNK업무시스템구축_엑셀/V2/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V2/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
@@ -1142,7 +1142,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>T-260407-3</t>
+          <t>T-260407-2</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>T-260303-2</t>
+          <t>T-260303-1</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>T-260409-2</t>
+          <t>T-260409-1</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>T-260409-3</t>
+          <t>T-260409-2</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>T-260410-2</t>
+          <t>T-260410-1</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>T-260410-3</t>
+          <t>T-260410-2</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>T-260403-6</t>
+          <t>T-260403-5</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>T-260408-7</t>
+          <t>T-260408-6</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>T-260408-8</t>
+          <t>T-260408-7</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>T-260408-9</t>
+          <t>T-260408-8</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>T-260408-10</t>
+          <t>T-260408-9</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>T-260406-2</t>
+          <t>T-260406-1</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>T-260406-3</t>
+          <t>T-260406-2</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>T-260406-4</t>
+          <t>T-260406-3</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>T-260406-5</t>
+          <t>T-260406-4</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>T-260406-6</t>
+          <t>T-260406-5</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>T-260406-7</t>
+          <t>T-260406-6</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>T-260406-12</t>
+          <t>T-260406-11</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>T-260406-13</t>
+          <t>T-260406-12</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>T-260406-14</t>
+          <t>T-260406-13</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>T-260406-15</t>
+          <t>T-260406-14</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>T-260327-2</t>
+          <t>T-260327-1</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>T-260327-3</t>
+          <t>T-260327-2</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>T-260327-4</t>
+          <t>T-260327-3</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>T-260327-5</t>
+          <t>T-260327-4</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>T-260327-6</t>
+          <t>T-260327-5</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>T-260327-7</t>
+          <t>T-260327-6</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>T-260331-2</t>
+          <t>T-260331-1</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>T-260324-5</t>
+          <t>T-260324-4</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>T-260401-4</t>
+          <t>T-260401-3</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>T-260323-2</t>
+          <t>T-260323-1</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>T-260323-3</t>
+          <t>T-260323-2</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>T-260323-4</t>
+          <t>T-260323-3</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>T-260323-5</t>
+          <t>T-260323-4</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>T-260323-6</t>
+          <t>T-260323-5</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>T-260406-16</t>
+          <t>T-260406-15</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>T-260408-2</t>
+          <t>T-260408-1</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>T-260408-3</t>
+          <t>T-260408-2</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>T-260408-4</t>
+          <t>T-260408-3</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>T-260406-8</t>
+          <t>T-260406-7</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>T-260406-9</t>
+          <t>T-260406-8</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>T-260406-10</t>
+          <t>T-260406-9</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>T-260406-11</t>
+          <t>T-260406-10</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>T-260407-2</t>
+          <t>T-260407-1</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>T-260409-4</t>
+          <t>T-260409-3</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>T-260409-5</t>
+          <t>T-260409-4</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>T-260409-6</t>
+          <t>T-260409-5</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>T-260324-8</t>
+          <t>T-260324-7</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>T-260407-4</t>
+          <t>T-260407-3</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>T-260324-10</t>
+          <t>T-260324-9</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>T-260410-4</t>
+          <t>T-260410-3</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>T-260413-2</t>
+          <t>T-260413-1</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>T-260413-3</t>
+          <t>T-260413-2</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>T-260413-4</t>
+          <t>T-260413-3</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>T-260413-5</t>
+          <t>T-260413-4</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>T-260409-7</t>
+          <t>T-260409-6</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>T-260409-8</t>
+          <t>T-260409-7</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>T-260409-9</t>
+          <t>T-260409-8</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>T-260409-10</t>
+          <t>T-260409-9</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>T-260409-11</t>
+          <t>T-260409-10</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>T-260407-5</t>
+          <t>T-260407-4</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>T-260413-6</t>
+          <t>T-260413-5</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>T-260413-7</t>
+          <t>T-260413-6</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>T-260413-8</t>
+          <t>T-260413-7</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>T-260413-9</t>
+          <t>T-260413-8</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>T-260413-10</t>
+          <t>T-260413-9</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>T-260413-11</t>
+          <t>T-260413-10</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>T-260331-3</t>
+          <t>T-260331-2</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>T-260324-9</t>
+          <t>T-260324-8</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>T-260413-12</t>
+          <t>T-260413-11</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>T-260413-17</t>
+          <t>T-260413-16</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>T-260413-18</t>
+          <t>T-260413-17</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>T-260413-19</t>
+          <t>T-260413-18</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>T-260415-2</t>
+          <t>T-260415-1</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>T-260415-3</t>
+          <t>T-260415-2</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>T-260413-13</t>
+          <t>T-260413-12</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>T-260413-14</t>
+          <t>T-260413-13</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>T-260413-15</t>
+          <t>T-260413-14</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>T-260413-16</t>
+          <t>T-260413-15</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>T-260408-5</t>
+          <t>T-260408-4</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>T-260408-6</t>
+          <t>T-260408-5</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>T-260414-2</t>
+          <t>T-260414-1</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>T-260413-20</t>
+          <t>T-260413-19</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>T-260413-21</t>
+          <t>T-260413-20</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>T-260414-3</t>
+          <t>T-260414-2</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>T-260226-2</t>
+          <t>T-260226-1</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>T-260226-3</t>
+          <t>T-260226-2</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>T-260331-12</t>
+          <t>T-260331-11</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>T-260425-2</t>
+          <t>T-260425-1</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
